--- a/artfynd/A 610-2025 artfynd.xlsx
+++ b/artfynd/A 610-2025 artfynd.xlsx
@@ -675,51 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96632291</v>
+        <v>96632494</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555403.8492052711</v>
+        <v>555327</v>
       </c>
       <c r="R2" t="n">
-        <v>6267704.390193205</v>
+        <v>6267637</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,24 +746,14 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>avverkningsanmälan  A 49276-2021</t>
+          <t>avverkningsanmälan A 49276-2021 på två olika lågor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -804,51 +781,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96632534</v>
+        <v>96632933</v>
       </c>
       <c r="B3" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -856,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555369.0043482085</v>
+        <v>555335</v>
       </c>
       <c r="R3" t="n">
-        <v>6267665.899290775</v>
+        <v>6267651</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,19 +852,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -934,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96632933</v>
+        <v>96897104</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555335.5049691289</v>
+        <v>555347</v>
       </c>
       <c r="R4" t="n">
-        <v>6267651.128400446</v>
+        <v>6267727</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,22 +955,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1055,51 +993,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96632352</v>
+        <v>96897114</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1107,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555341.4776157949</v>
+        <v>555318</v>
       </c>
       <c r="R5" t="n">
-        <v>6267743.25901562</v>
+        <v>6267711</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1137,27 +1061,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>avverkningsanmälan  A 49276-2021</t>
+          <t>avverkningsanmälan A 49276-2021</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,6 +1080,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1184,37 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96632412</v>
+        <v>97104018</v>
       </c>
       <c r="B6" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6031</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1227,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555244.7441253957</v>
+        <v>555324</v>
       </c>
       <c r="R6" t="n">
-        <v>6267622.378689363</v>
+        <v>6267628</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,22 +1167,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,6 +1184,26 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>barklös granlåga</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies # barklös granlåga</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1300,15 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96632226</v>
+        <v>96632265</v>
       </c>
       <c r="B7" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,26 +1231,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1343,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555423.7082941632</v>
+        <v>555412</v>
       </c>
       <c r="R7" t="n">
-        <v>6267706.304520692</v>
+        <v>6267696</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1376,19 +1300,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1420,15 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96632265</v>
+        <v>96632361</v>
       </c>
       <c r="B8" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555411.6891415737</v>
+        <v>555347</v>
       </c>
       <c r="R8" t="n">
-        <v>6267696.224928204</v>
+        <v>6267713</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1505,19 +1414,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1549,51 +1448,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96642266</v>
+        <v>96632389</v>
       </c>
       <c r="B9" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1601,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555335.5049691289</v>
+        <v>555302</v>
       </c>
       <c r="R9" t="n">
-        <v>6267651.128400446</v>
+        <v>6267697</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1634,19 +1528,14 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:00</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan  A 49276-2021</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1673,42 +1562,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96632494</v>
+        <v>96632428</v>
       </c>
       <c r="B10" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1716,10 +1609,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555326.2972762173</v>
+        <v>555277</v>
       </c>
       <c r="R10" t="n">
-        <v>6267637.227253479</v>
+        <v>6267596</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1749,24 +1642,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan A 49276-2021 på två olika lågor</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1794,47 +1672,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96632354</v>
+        <v>96632534</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1846,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555332.0100848441</v>
+        <v>555369</v>
       </c>
       <c r="R11" t="n">
-        <v>6267749.1981601</v>
+        <v>6267666</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1879,24 +1752,14 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>avverkningsanmälan  A 49276-2021</t>
+          <t>avverkningsanmälan A 49276-2021</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1905,6 +1768,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1923,51 +1787,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96632323</v>
+        <v>96632226</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1975,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555378.0310887995</v>
+        <v>555423</v>
       </c>
       <c r="R12" t="n">
-        <v>6267693.578394791</v>
+        <v>6267707</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2008,19 +1858,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2052,51 +1892,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96632532</v>
+        <v>96632412</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2104,10 +1930,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555369.0043482085</v>
+        <v>555245</v>
       </c>
       <c r="R13" t="n">
-        <v>6267665.899290775</v>
+        <v>6267622</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2137,32 +1963,18 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan A 49276-2021</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2181,49 +1993,44 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96642276</v>
+        <v>96642266</v>
       </c>
       <c r="B14" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2233,10 +2040,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555335.5049691289</v>
+        <v>555335</v>
       </c>
       <c r="R14" t="n">
-        <v>6267651.128400446</v>
+        <v>6267651</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2305,51 +2112,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96632361</v>
+        <v>96642276</v>
       </c>
       <c r="B15" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2357,10 +2159,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555346.8379668052</v>
+        <v>555335</v>
       </c>
       <c r="R15" t="n">
-        <v>6267713.564092278</v>
+        <v>6267651</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2392,7 +2194,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2402,12 +2204,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan  A 49276-2021</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2434,51 +2231,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96632428</v>
+        <v>96897129</v>
       </c>
       <c r="B16" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2486,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555277.1285311581</v>
+        <v>555318</v>
       </c>
       <c r="R16" t="n">
-        <v>6267595.792713273</v>
+        <v>6267711</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2516,22 +2308,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2540,7 +2322,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2559,15 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96632319</v>
+        <v>96624335</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2594,14 +2370,10 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2611,10 +2383,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555384.5351138981</v>
+        <v>555390</v>
       </c>
       <c r="R17" t="n">
-        <v>6267703.034320265</v>
+        <v>6267712</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2641,27 +2413,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>avverkningsanmälan  A 49276-2021</t>
+          <t>avverkningsanmälan A 49276-2021</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2670,6 +2432,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2688,47 +2451,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96632389</v>
+        <v>96632291</v>
       </c>
       <c r="B18" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2740,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555301.7634091571</v>
+        <v>555404</v>
       </c>
       <c r="R18" t="n">
-        <v>6267696.988241781</v>
+        <v>6267704</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2773,19 +2531,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2817,15 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96632439</v>
+        <v>96632319</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2852,7 +2595,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2869,10 +2612,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555308.545747662</v>
+        <v>555385</v>
       </c>
       <c r="R19" t="n">
-        <v>6267643.058041937</v>
+        <v>6267703</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2902,24 +2645,14 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>avverkningsanmälan A 49276-2021</t>
+          <t>avverkningsanmälan  A 49276-2021</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2928,7 +2661,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2947,15 +2679,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96624335</v>
+        <v>96632323</v>
       </c>
       <c r="B20" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2982,10 +2709,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -2995,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555389.3896112281</v>
+        <v>555378</v>
       </c>
       <c r="R20" t="n">
-        <v>6267711.917381245</v>
+        <v>6267694</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3025,27 +2756,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>avverkningsanmälan A 49276-2021</t>
+          <t>avverkningsanmälan  A 49276-2021</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3054,7 +2775,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3073,51 +2793,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96897129</v>
+        <v>96632439</v>
       </c>
       <c r="B21" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3125,10 +2840,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555318.7024559347</v>
+        <v>555308</v>
       </c>
       <c r="R21" t="n">
-        <v>6267710.990451365</v>
+        <v>6267643</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3155,22 +2870,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan A 49276-2021</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3179,6 +2889,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3197,42 +2908,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96897114</v>
+        <v>96632532</v>
       </c>
       <c r="B22" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3240,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555318.7024559347</v>
+        <v>555369</v>
       </c>
       <c r="R22" t="n">
-        <v>6267710.990451365</v>
+        <v>6267666</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3270,22 +2985,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3299,7 +3004,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3318,42 +3022,46 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>96897104</v>
+        <v>97104024</v>
       </c>
       <c r="B23" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3361,10 +3069,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555347.2240126507</v>
+        <v>555317</v>
       </c>
       <c r="R23" t="n">
-        <v>6267726.246950923</v>
+        <v>6267633</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3391,27 +3099,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan A 49276-2021</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3439,15 +3132,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>97104024</v>
+        <v>96632352</v>
       </c>
       <c r="B24" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3474,7 +3162,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3491,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555316.4072735655</v>
+        <v>555341</v>
       </c>
       <c r="R24" t="n">
-        <v>6267633.239108293</v>
+        <v>6267744</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3521,22 +3209,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan  A 49276-2021</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3545,7 +3228,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3564,42 +3246,46 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>97104018</v>
+        <v>96632354</v>
       </c>
       <c r="B25" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3607,10 +3293,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555324.7560841559</v>
+        <v>555332</v>
       </c>
       <c r="R25" t="n">
-        <v>6267628.387537828</v>
+        <v>6267749</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3637,22 +3323,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan  A 49276-2021</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3661,29 +3342,8 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>barklös granlåga</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies # barklös granlåga</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">

--- a/artfynd/A 610-2025 artfynd.xlsx
+++ b/artfynd/A 610-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632494</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632933</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96897104</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96897114</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97104018</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,6 +1361,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632265</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632361</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1559,6 +1599,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632389</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1669,6 +1714,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632428</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1784,6 +1834,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632534</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1889,6 +1944,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632226</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1990,6 +2050,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632412</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2109,6 +2174,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96642266</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2228,6 +2298,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96642276</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2337,6 +2412,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96897129</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2448,6 +2528,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96624335</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2562,6 +2647,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632291</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2676,6 +2766,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632319</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2790,6 +2885,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632323</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2904,6 +3004,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632352</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3018,6 +3123,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632354</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3133,6 +3243,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632439</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3247,6 +3362,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632532</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3357,8 +3477,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97104024</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>